--- a/data/trans_bre/P2A_senso_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P2A_senso_R-Clase-trans_bre.xlsx
@@ -660,32 +660,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 2,91</t>
+          <t>-0,75; 3,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 4,4</t>
+          <t>-1,02; 4,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 0,59</t>
+          <t>-1,1; 0,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 1,67</t>
+          <t>-1,56; 1,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-54,43; 478,37</t>
+          <t>-47,07; 593,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-54,09; 387,92</t>
+          <t>-46,81; 468,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-51,83; 169,95</t>
+          <t>-53,98; 132,34</t>
         </is>
       </c>
     </row>
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 0,51</t>
+          <t>-2,82; 0,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 2,22</t>
+          <t>-0,67; 2,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 2,4</t>
+          <t>-0,84; 2,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 1,34</t>
+          <t>-2,97; 1,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 108,83</t>
+          <t>-100,0; 150,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -790,12 +790,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-67,02; 1039,09</t>
+          <t>-68,73; 1039,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-71,62; 89,65</t>
+          <t>-70,56; 96,03</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 4,39</t>
+          <t>-0,68; 3,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 2,84</t>
+          <t>-1,66; 2,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 5,06</t>
+          <t>-1,6; 5,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 8,11</t>
+          <t>-0,63; 8,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 857,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-67,74; 237,02</t>
+          <t>-63,56; 219,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-33,57; 818,63</t>
+          <t>-27,4; 837,08</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 0,95</t>
+          <t>-1,39; 0,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 2,4</t>
+          <t>-0,83; 2,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 1,12</t>
+          <t>-0,85; 1,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 57,43</t>
+          <t>-0,49; 51,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-66,55; 76,39</t>
+          <t>-64,97; 74,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-37,05; 188,79</t>
+          <t>-34,71; 147,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-55,99; 196,57</t>
+          <t>-62,33; 167,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-21,67; 3336,17</t>
+          <t>-19,74; 3720,23</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 0,57</t>
+          <t>-3,34; 0,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 2,31</t>
+          <t>-0,53; 2,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 0,9</t>
+          <t>-1,88; 0,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 2,93</t>
+          <t>-1,23; 2,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-84,8; 61,61</t>
+          <t>-83,96; 79,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-41,6; 631,67</t>
+          <t>-40,31; 517,55</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-72,16; 131,77</t>
+          <t>-73,66; 112,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-29,19; 160,79</t>
+          <t>-28,76; 162,96</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 2,3</t>
+          <t>-0,58; 2,29</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 1,75</t>
+          <t>-2,74; 1,74</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 1,12</t>
+          <t>-1,13; 1,14</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,67</t>
+          <t>1,24; 3,69</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-45,92; —</t>
+          <t>-38,96; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-68,34; 280,71</t>
+          <t>-64,6; 319,84</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-78,73; —</t>
+          <t>-74,27; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>50,36; 3861,38</t>
+          <t>30,68; 4858,52</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,75</t>
+          <t>-0,55; 0,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 1,11</t>
+          <t>-0,18; 1,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,54</t>
+          <t>-0,5; 0,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,49; 22,88</t>
+          <t>0,49; 23,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-26,14; 61,52</t>
+          <t>-30,19; 55,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-11,1; 82,71</t>
+          <t>-10,71; 85,17</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-37,32; 71,72</t>
+          <t>-37,43; 78,1</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>20,99; 1108,44</t>
+          <t>19,7; 1046,0</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_senso_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P2A_senso_R-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>0,27</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>13,63%</t>
         </is>
       </c>
     </row>
@@ -660,32 +660,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 3,18</t>
+          <t>-0,96; 2,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 4,19</t>
+          <t>-0,81; 4,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 0,51</t>
+          <t>-1,22; 0,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 1,63</t>
+          <t>-1,34; 1,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-47,07; 593,19</t>
+          <t>-63,85; 439,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-46,81; 468,95</t>
+          <t>-39,21; 502,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-53,98; 132,34</t>
+          <t>-46,78; 160,03</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,61</t>
+          <t>-0,56</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-22,23%</t>
+          <t>-20,13%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 0,48</t>
+          <t>-2,96; 0,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 2,28</t>
+          <t>-0,69; 2,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 2,37</t>
+          <t>-0,79; 2,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 1,36</t>
+          <t>-2,86; 1,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 150,25</t>
+          <t>-100,0; 99,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 1000,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-68,73; 1039,26</t>
+          <t>-68,61; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-70,56; 96,03</t>
+          <t>-68,69; 109,0</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,17</t>
+          <t>1,28</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>107,94%</t>
+          <t>41,31%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 3,96</t>
+          <t>-0,67; 3,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 2,72</t>
+          <t>-1,64; 2,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 5,18</t>
+          <t>-1,54; 5,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 8,83</t>
+          <t>-1,6; 7,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 857,71</t>
+          <t>-100,0; 1153,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-63,56; 219,42</t>
+          <t>-65,39; 200,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-27,4; 837,08</t>
+          <t>-50,56; 353,55</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20,41</t>
+          <t>-0,34</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>883,99%</t>
+          <t>-13,14%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 0,92</t>
+          <t>-1,39; 1,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 2,04</t>
+          <t>-0,99; 2,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 1,11</t>
+          <t>-0,74; 1,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 51,33</t>
+          <t>-1,67; 0,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-64,97; 74,59</t>
+          <t>-64,91; 83,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-34,71; 147,85</t>
+          <t>-39,69; 143,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-62,33; 167,79</t>
+          <t>-60,47; 254,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-19,74; 3720,23</t>
+          <t>-49,36; 41,85</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,09</t>
+          <t>1,88</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>69,21%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 0,73</t>
+          <t>-3,17; 0,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 2,15</t>
+          <t>-0,54; 2,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 0,87</t>
+          <t>-1,87; 0,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 2,96</t>
+          <t>-0,1; 3,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-83,96; 79,72</t>
+          <t>-82,96; 64,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-40,31; 517,55</t>
+          <t>-39,55; 555,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-73,66; 112,33</t>
+          <t>-71,86; 129,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-28,76; 162,96</t>
+          <t>-5,39; 207,26</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,54</t>
+          <t>2,23</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>445,95%</t>
+          <t>175,04%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 2,29</t>
+          <t>-0,56; 2,31</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 1,74</t>
+          <t>-2,97; 1,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 1,14</t>
+          <t>-1,35; 1,16</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,69</t>
+          <t>-0,36; 3,9</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-38,96; —</t>
+          <t>-39,01; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-64,6; 319,84</t>
+          <t>-68,13; 439,42</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-74,27; —</t>
+          <t>-82,75; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>30,68; 4858,52</t>
+          <t>-33,46; 1444,02</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6,28</t>
+          <t>0,67</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>281,28%</t>
+          <t>26,51%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 0,73</t>
+          <t>-0,49; 0,72</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 1,13</t>
+          <t>-0,23; 1,18</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,57</t>
+          <t>-0,48; 0,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,49; 23,68</t>
+          <t>-0,07; 1,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-30,19; 55,15</t>
+          <t>-26,49; 58,48</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,71; 85,17</t>
+          <t>-12,49; 84,66</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-37,43; 78,1</t>
+          <t>-36,58; 81,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>19,7; 1046,0</t>
+          <t>-2,54; 68,51</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_senso_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P2A_senso_R-Clase-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad sensorial</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad sensorial</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
